--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488265_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488265_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3055</v>
+        <v>2.0636</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0653</v>
+        <v>0.1853</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3707</v>
+        <v>1.8783</v>
       </c>
       <c r="G2" t="n">
         <v>1.6805</v>
@@ -610,13 +610,13 @@
         <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1242</v>
+        <v>0.8823</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5397</v>
+        <v>0.7903</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5844</v>
+        <v>0.092</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3139</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9573</v>
+        <v>1.908</v>
       </c>
       <c r="E3" t="n">
         <v>0.1032</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8541</v>
+        <v>1.8048</v>
       </c>
       <c r="G3" t="n">
         <v>-0.4347</v>
@@ -688,13 +688,13 @@
         <v>1.4823</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1634</v>
+        <v>-0.2126</v>
       </c>
       <c r="T3" t="n">
         <v>0.1816</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.345</v>
+        <v>-0.3942</v>
       </c>
       <c r="V3" t="n">
         <v>1.2583</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. ROSA CABRERA</t>
+          <t>Á. CHAPARRO CARRASCO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3153</v>
+        <v>1.2662</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7138</v>
+        <v>1.2662</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6015</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.5579</v>
+        <v>1.2662</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6853</v>
+        <v>0.6441</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8725000000000001</v>
+        <v>0.6221</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4415</v>
+        <v>1.2662</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8844</v>
+        <v>0.6441</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.3258</v>
+        <v>0.6221</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1164</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5697</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4533</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4823</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3167</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.0817</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Á. CHAPARRO CARRASCO</t>
+          <t>J. ROSA CABRERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2662</v>
+        <v>0.4454</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2662</v>
+        <v>-0.1561</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.6015</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2662</v>
+        <v>-1.5579</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6441</v>
+        <v>-0.6853</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6221</v>
+        <v>-0.8725000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2662</v>
+        <v>-0.4415</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6441</v>
+        <v>0.8844</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6221</v>
+        <v>-1.3258</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-1.1164</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-1.5697</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.4533</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.4823</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.4469</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.2119</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.235</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4734</v>
+        <v>0.381</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.12</v>
+        <v>-1.1632</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5935</v>
+        <v>1.5442</v>
       </c>
       <c r="G6" t="n">
         <v>0.6152</v>
@@ -922,13 +922,13 @@
         <v>1.297</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3275</v>
+        <v>-0.42</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2151</v>
+        <v>0.1719</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5427</v>
+        <v>-0.5919</v>
       </c>
       <c r="V6" t="n">
         <v>0.0005</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7687</v>
+        <v>-0.2358</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.222</v>
+        <v>-0.9599</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4533</v>
+        <v>0.7241</v>
       </c>
       <c r="G7" t="n">
         <v>0.0737</v>
@@ -1000,13 +1000,13 @@
         <v>1.6676</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3243</v>
+        <v>0.2086</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1131</v>
+        <v>0.1489</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2112</v>
+        <v>0.0597</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2593</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8502999999999999</v>
+        <v>-1.4986</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7406</v>
+        <v>-2.6105</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8903</v>
+        <v>1.1119</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3175</v>
@@ -1078,13 +1078,13 @@
         <v>2.594</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3739</v>
+        <v>0.7256</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1153</v>
+        <v>1.2454</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.5198</v>
       </c>
       <c r="V8" t="n">
         <v>-2.2037</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0462</v>
+        <v>-3.2361</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8149</v>
+        <v>-2.054</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2313</v>
+        <v>-1.1821</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0479</v>
@@ -1156,13 +1156,13 @@
         <v>0.3706</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2604</v>
+        <v>0.0706</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1604</v>
+        <v>-0.0786</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1</v>
+        <v>0.1492</v>
       </c>
       <c r="V9" t="n">
         <v>-2.5176</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. QUINTERO DE ARMAS</t>
+          <t>I. FERNANDEZ MEGIAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5254</v>
+        <v>-3.2383</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2254</v>
+        <v>-2.9107</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3</v>
+        <v>-0.3276</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.642</v>
+        <v>-2.21</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4438</v>
+        <v>-0.7277</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1981</v>
+        <v>-1.4823</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.9371</v>
+        <v>-2.1525</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6314</v>
+        <v>-0.1939</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3057</v>
+        <v>-1.9586</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7048</v>
+        <v>-0.0575</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8124</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1076</v>
+        <v>0.4763</v>
       </c>
       <c r="P10" t="n">
         <v>-0.3706</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9264</v>
+        <v>-1.297</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.9264</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5128</v>
+        <v>-0.0283</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3619</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.151</v>
+        <v>-0.5671</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. MALINIC</t>
+          <t>F. QUINTERO DE ARMAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7959</v>
+        <v>-3.2808</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3776</v>
+        <v>-2.9316</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5817</v>
+        <v>-0.3492</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6437</v>
+        <v>-2.642</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9893999999999999</v>
+        <v>-1.4438</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3457</v>
+        <v>-1.1981</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2322</v>
+        <v>-1.9371</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2322</v>
+        <v>-0.6314</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-1.3057</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4115</v>
+        <v>-0.7048</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7573</v>
+        <v>-0.8124</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3457</v>
+        <v>0.1076</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.7793</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.891</v>
+        <v>-0.9264</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1117</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5715</v>
+        <v>-0.2683</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3756</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.196</v>
+        <v>-0.2002</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9444</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. FERNANDEZ MEGIAS</t>
+          <t>M. MALINIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.17</v>
+        <v>-4.1526</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5962</v>
+        <v>-4.5619</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5738</v>
+        <v>0.4093</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.21</v>
+        <v>-0.6437</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7277</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.4823</v>
+        <v>0.3457</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.1525</v>
+        <v>-0.2322</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1939</v>
+        <v>-0.2322</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9586</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0575</v>
+        <v>-0.4115</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-0.7573</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4763</v>
+        <v>0.3457</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3706</v>
+        <v>-2.7793</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.297</v>
+        <v>-3.891</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.96</v>
+        <v>0.2148</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1467</v>
+        <v>0.1912</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8133</v>
+        <v>0.0236</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6294</v>
+        <v>-0.9444</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6294</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.0021</v>
+        <v>-8.5162</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.815</v>
+        <v>-9.2798</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8129</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-7.4095</v>
@@ -1468,13 +1468,13 @@
         <v>1.4823</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.111</v>
+        <v>0.3749</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2584</v>
+        <v>0.2767</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1475</v>
+        <v>0.0982</v>
       </c>
       <c r="V13" t="n">
         <v>0.0007</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-18.8409</v>
+        <v>-18.0942</v>
       </c>
       <c r="E14" t="n">
-        <v>-25.8938</v>
+        <v>-25.073</v>
       </c>
       <c r="F14" t="n">
-        <v>7.052899999999999</v>
+        <v>6.978800000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-12.6276</v>
@@ -1516,7 +1516,7 @@
         <v>-7.7704</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.856999999999999</v>
+        <v>-4.857</v>
       </c>
       <c r="J14" t="n">
         <v>-12.2454</v>
@@ -1528,13 +1528,13 @@
         <v>-9.6044</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.382</v>
+        <v>-0.3820000000000001</v>
       </c>
       <c r="N14" t="n">
         <v>-5.1295</v>
       </c>
       <c r="O14" t="n">
-        <v>4.747400000000001</v>
+        <v>4.7474</v>
       </c>
       <c r="P14" t="n">
         <v>-1.8529</v>
@@ -1546,13 +1546,13 @@
         <v>14.6377</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2477</v>
+        <v>2.994499999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>3.7893</v>
+        <v>4.609999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.5417</v>
+        <v>-1.6155</v>
       </c>
       <c r="V14" t="n">
         <v>-6.6083</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.3376</v>
+        <v>9.3445</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4656</v>
+        <v>4.5635</v>
       </c>
       <c r="F15" t="n">
-        <v>4.872</v>
+        <v>4.781</v>
       </c>
       <c r="G15" t="n">
         <v>4.5797</v>
@@ -1624,13 +1624,13 @@
         <v>1.8529</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.241</v>
+        <v>-0.2341</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2773</v>
+        <v>-0.1794</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0363</v>
+        <v>-0.0547</v>
       </c>
       <c r="V15" t="n">
         <v>3.146</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.968</v>
+        <v>6.5172</v>
       </c>
       <c r="E16" t="n">
         <v>4.6941</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2739</v>
+        <v>1.8231</v>
       </c>
       <c r="G16" t="n">
         <v>4.3878</v>
@@ -1702,13 +1702,13 @@
         <v>1.297</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9757</v>
+        <v>-0.4265</v>
       </c>
       <c r="T16" t="n">
         <v>-0.0584</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9172</v>
+        <v>-0.3681</v>
       </c>
       <c r="V16" t="n">
         <v>1.2589</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.4609</v>
+        <v>5.4718</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.1371</v>
+        <v>-1.0599</v>
       </c>
       <c r="F17" t="n">
-        <v>6.598</v>
+        <v>6.5316</v>
       </c>
       <c r="G17" t="n">
         <v>6.898</v>
@@ -1780,13 +1780,13 @@
         <v>2.7793</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.825</v>
+        <v>-0.8142</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.4226</v>
+        <v>-0.3454</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4025</v>
+        <v>-0.4689</v>
       </c>
       <c r="V17" t="n">
         <v>0.3144</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. GEDEAO YIMBU</t>
+          <t>F. GARRIDO SOTO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8285</v>
+        <v>2.8382</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.6537</v>
+        <v>-0.3868</v>
       </c>
       <c r="F18" t="n">
-        <v>4.4822</v>
+        <v>3.2249</v>
       </c>
       <c r="G18" t="n">
-        <v>0.756</v>
+        <v>0.9213</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0428</v>
+        <v>-0.4259</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7989</v>
+        <v>1.3472</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5597</v>
+        <v>-0.4483</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.6841</v>
+        <v>-0.4898</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1244</v>
+        <v>0.0415</v>
       </c>
       <c r="M18" t="n">
-        <v>2.3158</v>
+        <v>1.3696</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6413</v>
+        <v>0.0639</v>
       </c>
       <c r="O18" t="n">
-        <v>1.6744</v>
+        <v>1.3057</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3706</v>
+        <v>2.0382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8529</v>
+        <v>-0.1853</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4823</v>
+        <v>2.2234</v>
       </c>
       <c r="S18" t="n">
-        <v>2.443</v>
+        <v>-0.1212</v>
       </c>
       <c r="T18" t="n">
-        <v>2.3889</v>
+        <v>0.2469</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0542</v>
+        <v>-0.3681</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. GARRIDO SOTO</t>
+          <t>J. MIAVIVULULU NZIKULU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.6841</v>
+        <v>1.4942</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5826</v>
+        <v>-1.7305</v>
       </c>
       <c r="F19" t="n">
-        <v>3.2667</v>
+        <v>3.2247</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9213</v>
+        <v>2.745</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4259</v>
+        <v>0.1967</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3472</v>
+        <v>2.5482</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4483</v>
+        <v>1.8191</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4898</v>
+        <v>0.5536</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0415</v>
+        <v>1.2655</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3696</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0639</v>
+        <v>-0.3568</v>
       </c>
       <c r="O19" t="n">
-        <v>1.3057</v>
+        <v>1.2827</v>
       </c>
       <c r="P19" t="n">
-        <v>2.0382</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1853</v>
+        <v>-3.891</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2234</v>
+        <v>2.4087</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2753</v>
+        <v>-0.7129</v>
       </c>
       <c r="T19" t="n">
-        <v>0.051</v>
+        <v>0.0271</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3263</v>
+        <v>-0.7399</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.9444</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MIAVIVULULU NZIKULU</t>
+          <t>M. GEDEAO YIMBU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6403</v>
+        <v>0.9988</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4367</v>
+        <v>-3.3185</v>
       </c>
       <c r="F20" t="n">
-        <v>3.0769</v>
+        <v>4.3173</v>
       </c>
       <c r="G20" t="n">
-        <v>2.745</v>
+        <v>0.756</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1967</v>
+        <v>-1.0428</v>
       </c>
       <c r="I20" t="n">
-        <v>2.5482</v>
+        <v>1.7989</v>
       </c>
       <c r="J20" t="n">
-        <v>1.8191</v>
+        <v>-1.5597</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5536</v>
+        <v>-1.6841</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2655</v>
+        <v>0.1244</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9258999999999999</v>
+        <v>2.3158</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3568</v>
+        <v>0.6413</v>
       </c>
       <c r="O20" t="n">
-        <v>1.2827</v>
+        <v>1.6744</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.4823</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.891</v>
+        <v>-1.8529</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4087</v>
+        <v>1.4823</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5668</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3209</v>
+        <v>0.7241</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8877</v>
+        <v>-0.1107</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9444</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3144</v>
+        <v>-0.63</v>
       </c>
       <c r="X20" t="n">
         <v>0.63</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3186</v>
+        <v>0.9554</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1153</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4338</v>
+        <v>1.4831</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3231</v>
@@ -2092,13 +2092,13 @@
         <v>0.9264</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7295</v>
+        <v>-0.0926</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.383</v>
+        <v>0.2046</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3465</v>
+        <v>-0.2972</v>
       </c>
       <c r="V21" t="n">
         <v>0.63</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. MOLINA LOPEZ</t>
+          <t>C. ALVAREZ GONZALEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5951</v>
+        <v>-0.5171</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4106</v>
+        <v>-0.4688</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8155</v>
+        <v>-0.0483</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4506</v>
+        <v>-0.3023</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2755</v>
+        <v>-0.0412</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8249</v>
+        <v>-0.2611</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2428</v>
+        <v>-0.6099</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2843</v>
+        <v>0.0429</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0415</v>
+        <v>-0.6529</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7922</v>
+        <v>0.3076</v>
       </c>
       <c r="N22" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7834</v>
+        <v>0.3917</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.297</v>
+        <v>0.3706</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.3706</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1525</v>
+        <v>0.0441</v>
       </c>
       <c r="T22" t="n">
-        <v>1.685</v>
+        <v>0.1411</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5325</v>
+        <v>-0.097</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. ALVAREZ GONZALEZ</t>
+          <t>J. PINILLA NUNEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8114</v>
+        <v>-1.214</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6646</v>
+        <v>-0.8012</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1468</v>
+        <v>-0.4128</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3023</v>
+        <v>-2.9368</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0412</v>
+        <v>-0.8431999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2611</v>
+        <v>-2.0937</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6099</v>
+        <v>-2.4411</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0429</v>
+        <v>-0.524</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6529</v>
+        <v>-1.9171</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3076</v>
+        <v>-0.4957</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.3191</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3917</v>
+        <v>-0.1766</v>
       </c>
       <c r="P23" t="n">
         <v>0.3706</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.1117</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3706</v>
+        <v>1.4823</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2502</v>
+        <v>-0.221</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0547</v>
+        <v>-0.0805</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1955</v>
+        <v>-0.1405</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6294</v>
+        <v>1.5733</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.8321</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6294</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.0588</v>
+        <v>-1.3285</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8524</v>
+        <v>-3.0483</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7936</v>
+        <v>1.7197</v>
       </c>
       <c r="G24" t="n">
         <v>-2.2307</v>
@@ -2326,13 +2326,13 @@
         <v>0.7411</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4308</v>
+        <v>0.161</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3246</v>
+        <v>0.1287</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1062</v>
+        <v>0.0323</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. PINILLA NUNEZ</t>
+          <t>M. MOLINA LOPEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.9241</v>
+        <v>-1.5738</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.4867</v>
+        <v>-2.4879</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4374</v>
+        <v>0.914</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.9368</v>
+        <v>-0.4506</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.8431999999999999</v>
+        <v>-1.2755</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.0937</v>
+        <v>0.8249</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.4411</v>
+        <v>-1.2428</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.524</v>
+        <v>-1.2843</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.9171</v>
+        <v>0.0415</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.4957</v>
+        <v>0.7922</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.3191</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.1766</v>
+        <v>0.7834</v>
       </c>
       <c r="P25" t="n">
-        <v>0.3706</v>
+        <v>-1.297</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1117</v>
+        <v>-1.8529</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4823</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9312</v>
+        <v>0.1738</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.766</v>
+        <v>0.6078</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1652</v>
+        <v>-0.434</v>
       </c>
       <c r="V25" t="n">
-        <v>1.5733</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.8321</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.6817</v>
+        <v>-3.1669</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.7243</v>
+        <v>-2.3325</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.9575</v>
+        <v>-0.8344</v>
       </c>
       <c r="G26" t="n">
         <v>-1.3362</v>
@@ -2482,13 +2482,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2338</v>
+        <v>0.281</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0547</v>
+        <v>0.337</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1791</v>
+        <v>-0.056</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6294</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>19.1669</v>
+        <v>19.81980000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>-6.904299999999999</v>
+        <v>-6.904499999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>26.0709</v>
+        <v>26.7239</v>
       </c>
       <c r="G27" t="n">
         <v>12.7081</v>
@@ -2533,10 +2533,10 @@
         <v>4.685</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5042000000000011</v>
+        <v>0.5041999999999998</v>
       </c>
       <c r="K27" t="n">
-        <v>5.3819</v>
+        <v>5.381900000000001</v>
       </c>
       <c r="L27" t="n">
         <v>-4.8781</v>
@@ -2548,7 +2548,7 @@
         <v>2.6411</v>
       </c>
       <c r="O27" t="n">
-        <v>9.562799999999999</v>
+        <v>9.562800000000001</v>
       </c>
       <c r="P27" t="n">
         <v>1.8529</v>
@@ -2560,22 +2560,22 @@
         <v>16.6758</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.0022</v>
+        <v>-1.3492</v>
       </c>
       <c r="T27" t="n">
-        <v>1.7537</v>
+        <v>1.7536</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.7558</v>
+        <v>-3.1028</v>
       </c>
       <c r="V27" t="n">
-        <v>6.608199999999998</v>
+        <v>6.6082</v>
       </c>
       <c r="W27" t="n">
         <v>5.6609</v>
       </c>
       <c r="X27" t="n">
-        <v>0.9473</v>
+        <v>0.9473000000000003</v>
       </c>
     </row>
   </sheetData>
